--- a/CATCH_Compliance_Dashboard.xlsx
+++ b/CATCH_Compliance_Dashboard.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance Gaps" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Compliance Dashboard'!$A$2:$N$2</definedName>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +50,14 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +94,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -105,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -114,16 +127,46 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -494,7 +537,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -506,7 +549,7 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
@@ -592,137 +635,137 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>CATCH Care Transitions Operations Manual.pdf</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Care Transitions</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>See Document</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Not Found</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Not Found</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>✘ Missing</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>✘ Missing</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>✘ Missing</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>⚠ Review Needed</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>Missing Effective Date; Missing End Date; Missing Scope of Work</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>CATCH Greater Houston PSA 2025-2030,CW2595700 - signed.pdf</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Greater Houston PSA</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>corporation</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>December 1, 2025</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Not Found</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>⚠ Review Needed</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>Missing End Date</t>
         </is>
@@ -732,137 +775,137 @@
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>CATCH HHD MSA Final.docx</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>HHD MSA</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Transition Care of Houston</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Not Found</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Not Found</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>⚠ Review Needed</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>Missing Effective Date; Missing End Date</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>CATCH Insurance Proposal from USI.pdf</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>your insurance company</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Not Found</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Not Found</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>⚠ Review Needed</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Missing Effective Date; Missing End Date</t>
         </is>
@@ -872,137 +915,137 @@
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>CATCH and PrognosUS DUA FINAL 3.19.26.docx.pdf</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>PrognosUS DUA</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>See Document</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>March 19, 2026</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Not Found</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>⚠ Review Needed</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>Missing End Date</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>CATCH_ISF_3526_FINALdocx.pdf</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>ISF</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>between CATCH Greater</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>March 12, 2026</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Not Found</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>⚠ Review Needed</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>Missing End Date</t>
         </is>
@@ -1012,137 +1055,137 @@
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Common Spirit 2026.pdf</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Dua</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>See Document</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Not Found</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>March 31, 2027</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>⚠ Review Needed</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>Missing Effective Date</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Cumulus Fully Executed Master Subscription Agreement.pdf</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Cumulus MSA</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>the parties have relied on these limitations in determining whether to enter into this Agreement</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Not Found</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Not Found</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>✘ Missing</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>✘ Missing</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>⚠ Review Needed</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>Missing Effective Date; Missing End Date; Missing Scope of Work</t>
         </is>
@@ -1152,137 +1195,137 @@
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>DPP SupplierAgreementGeneral CATCH FL03.13.26.docx</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>DPP Supplier</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>any of its clients</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Not Found</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Not Found</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>⚠ Review Needed</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>Missing Effective Date; Missing End Date</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Harmonic Health GUIDE Partner Organization Agreement_CATCH.pdf</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Harmonic Health GUIDE</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Partner with respect to the subject matter hereof</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>October 13, 2025</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>June 30, 2026</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>✘ Missing</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>⚠ Review Needed</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="N12" s="7" t="inlineStr">
         <is>
           <t>Missing Scope of Work</t>
         </is>
@@ -1292,67 +1335,67 @@
       <c r="A13" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Harmonic_CATCH_Care_Management_Agreement_Final_12926docx.pdf</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Harmonic Care Management</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Harmonic with respect to care</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>February 2, 2026</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>December 31, 2026</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>✔ Found</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>✔ Found</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>✔ Compliant</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1365,4 +1408,929 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="35" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Compliance Gaps — Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Document Name</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Gap Category</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>CATCH Care Transitions Operations Manual.pdf</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Care Transitions</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Missing Effective Date</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>CATCH Care Transitions Operations Manual.pdf</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Care Transitions</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Missing End Date</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>CATCH Care Transitions Operations Manual.pdf</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Care Transitions</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Missing Scope of Work</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>CATCH Greater Houston PSA 2025-2030,CW2595700 - signed.pdf</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Greater Houston PSA</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Missing End Date</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>CATCH HHD MSA Final.docx</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>HHD MSA</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Missing Effective Date</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CATCH HHD MSA Final.docx</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>HHD MSA</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Missing End Date</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>CATCH Insurance Proposal from USI.pdf</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Missing Effective Date</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>CATCH Insurance Proposal from USI.pdf</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Missing End Date</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>CATCH and PrognosUS DUA FINAL 3.19.26.docx.pdf</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>PrognosUS DUA</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Missing End Date</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>CATCH_ISF_3526_FINALdocx.pdf</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Missing End Date</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Common Spirit 2026.pdf</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Dua</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Missing Effective Date</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Cumulus Fully Executed Master Subscription Agreement.pdf</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Cumulus MSA</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Missing Effective Date</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="25" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Cumulus Fully Executed Master Subscription Agreement.pdf</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Cumulus MSA</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Missing End Date</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="25" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Cumulus Fully Executed Master Subscription Agreement.pdf</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Cumulus MSA</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Missing Scope of Work</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="25" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>DPP SupplierAgreementGeneral CATCH FL03.13.26.docx</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>DPP Supplier</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Missing Effective Date</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="25" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>DPP SupplierAgreementGeneral CATCH FL03.13.26.docx</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>DPP Supplier</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Missing End Date</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="25" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Harmonic Health GUIDE Partner Organization Agreement_CATCH.pdf</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Harmonic Health GUIDE</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Missing Scope of Work</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Gap Summary by Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Gap Category</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t># Documents Affected</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Missing Effective Date</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Missing End Date</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Missing Signatures</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>✔ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Missing Scope of Work</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Missing Insurance Clause</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>✔ OK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="35" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Compliance Dashboard — Run History</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Run #</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Date &amp; Time</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Documents Found</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Review Needed</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:34:08</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>11 document change(s) detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Document Change Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Run #</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Date &amp; Time</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Change Type</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Document Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:34:08</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>CATCH Insurance Proposal from USI.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:34:08</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>CATCH_ISF_3526_FINALdocx.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:34:08</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>CATCH and PrognosUS DUA FINAL 3.19.26.docx.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:34:08</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>DPP SupplierAgreementGeneral CATCH FL03.13.26.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:34:08</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Harmonic Health GUIDE Partner Organization Agreement_CATCH.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:34:08</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>CATCH HHD MSA Final.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:34:08</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>CATCH Greater Houston PSA 2025-2030,CW2595700 - signed.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:34:08</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Harmonic_CATCH_Care_Management_Agreement_Final_12926docx.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:34:08</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>CATCH Care Transitions Operations Manual.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:34:08</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Common Spirit 2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:34:08</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Cumulus Fully Executed Master Subscription Agreement.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/CATCH_Compliance_Dashboard.xlsx
+++ b/CATCH_Compliance_Dashboard.xlsx
@@ -538,7 +538,7 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -712,7 +712,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Greater Houston PSA</t>
+          <t>CHI/PIN</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>HHD MSA</t>
+          <t>GUIDE, CHI/PIN</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>PrognosUS DUA</t>
+          <t>GUIDE</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CHI/PIN</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Dua</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Cumulus MSA</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>DPP Supplier</t>
+          <t>DPP</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Harmonic Health GUIDE</t>
+          <t>GUIDE</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Harmonic Care Management</t>
+          <t>GUIDE</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1416,20 +1416,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Compliance Gaps — Detail</t>
+          <t>Compliance Gaps — Detail &amp; Resolution</t>
         </is>
       </c>
     </row>
@@ -1459,8 +1460,13 @@
           <t>Severity</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="6" t="n">
         <v>1</v>
       </c>
@@ -1484,8 +1490,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Locate or request original signed agreement. Add effective date to document metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>2</v>
       </c>
@@ -1509,8 +1520,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Confirm contract term with vendor/partner and record expiration date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="6" t="n">
         <v>3</v>
       </c>
@@ -1534,8 +1550,13 @@
           <t>Medium</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="25" customHeight="1">
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Request Scope of Work addendum from vendor or legal team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>4</v>
       </c>
@@ -1546,7 +1567,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Greater Houston PSA</t>
+          <t>CHI/PIN</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1559,8 +1580,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="25" customHeight="1">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Confirm contract term with vendor/partner and record expiration date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="6" t="n">
         <v>5</v>
       </c>
@@ -1571,7 +1597,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>HHD MSA</t>
+          <t>GUIDE, CHI/PIN</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -1584,8 +1610,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="25" customHeight="1">
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Locate or request original signed agreement. Add effective date to document metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="3" t="n">
         <v>6</v>
       </c>
@@ -1596,7 +1627,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>HHD MSA</t>
+          <t>GUIDE, CHI/PIN</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1609,8 +1640,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="25" customHeight="1">
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Confirm contract term with vendor/partner and record expiration date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>7</v>
       </c>
@@ -1621,7 +1657,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -1634,8 +1670,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="25" customHeight="1">
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Locate or request original signed agreement. Add effective date to document metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>8</v>
       </c>
@@ -1646,7 +1687,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1659,8 +1700,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="25" customHeight="1">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Confirm contract term with vendor/partner and record expiration date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>9</v>
       </c>
@@ -1671,7 +1717,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>PrognosUS DUA</t>
+          <t>GUIDE</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -1684,8 +1730,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="25" customHeight="1">
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Confirm contract term with vendor/partner and record expiration date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>10</v>
       </c>
@@ -1696,7 +1747,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CHI/PIN</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1709,8 +1760,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="25" customHeight="1">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Confirm contract term with vendor/partner and record expiration date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>11</v>
       </c>
@@ -1721,7 +1777,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Dua</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -1734,8 +1790,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="25" customHeight="1">
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Locate or request original signed agreement. Add effective date to document metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>12</v>
       </c>
@@ -1746,7 +1807,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Cumulus MSA</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1759,8 +1820,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="25" customHeight="1">
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Locate or request original signed agreement. Add effective date to document metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>13</v>
       </c>
@@ -1771,7 +1837,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Cumulus MSA</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -1784,8 +1850,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="25" customHeight="1">
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Confirm contract term with vendor/partner and record expiration date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
       <c r="A16" s="3" t="n">
         <v>14</v>
       </c>
@@ -1796,7 +1867,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Cumulus MSA</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1809,8 +1880,13 @@
           <t>Medium</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="25" customHeight="1">
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Request Scope of Work addendum from vendor or legal team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
       <c r="A17" s="6" t="n">
         <v>15</v>
       </c>
@@ -1821,7 +1897,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>DPP Supplier</t>
+          <t>DPP</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -1834,8 +1910,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="25" customHeight="1">
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Locate or request original signed agreement. Add effective date to document metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
       <c r="A18" s="3" t="n">
         <v>16</v>
       </c>
@@ -1846,7 +1927,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>DPP Supplier</t>
+          <t>DPP</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1859,8 +1940,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="25" customHeight="1">
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Confirm contract term with vendor/partner and record expiration date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
       <c r="A19" s="6" t="n">
         <v>17</v>
       </c>
@@ -1871,7 +1957,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Harmonic Health GUIDE</t>
+          <t>GUIDE</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -1882,6 +1968,11 @@
       <c r="E19" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Request Scope of Work addendum from vendor or legal team.</t>
         </is>
       </c>
     </row>
@@ -1908,8 +1999,13 @@
           <t>Severity</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Standard Resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="35" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Missing Effective Date</t>
@@ -1923,8 +2019,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Locate or request original signed agreement. Add effective date to document metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="35" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Missing End Date</t>
@@ -1938,8 +2039,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Confirm contract term with vendor/partner and record expiration date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="35" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
         <is>
           <t>Missing Signatures</t>
@@ -1955,8 +2061,13 @@
           <t>✔ OK</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Obtain authorized signatures from all parties. Ensure document is fully executed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="35" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Missing Scope of Work</t>
@@ -1970,8 +2081,13 @@
           <t>Medium</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>Request Scope of Work addendum from vendor or legal team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="35" customHeight="1">
       <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Missing Insurance Clause</t>
@@ -1985,13 +2101,18 @@
       <c r="C28" s="13" t="inlineStr">
         <is>
           <t>✔ OK</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>Request certificate of insurance from vendor or add insurance clause via amendment.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2003,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2011,7 +2132,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
@@ -2055,11 +2176,11 @@
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17 12:34:08</t>
+          <t>2026-06-17 13:02:47</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -2073,56 +2194,60 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
+          <t>No changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:34:08</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
           <t>11 document change(s) detected</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Document Change Log</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Run #</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Date &amp; Time</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Change Type</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Document Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-17 12:34:08</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>CATCH Insurance Proposal from USI.pdf</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2267,7 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>CATCH_ISF_3526_FINALdocx.pdf</t>
+          <t>CATCH Insurance Proposal from USI.pdf</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2287,7 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>CATCH and PrognosUS DUA FINAL 3.19.26.docx.pdf</t>
+          <t>CATCH_ISF_3526_FINALdocx.pdf</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2307,7 @@
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>DPP SupplierAgreementGeneral CATCH FL03.13.26.docx</t>
+          <t>CATCH and PrognosUS DUA FINAL 3.19.26.docx.pdf</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2327,7 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Harmonic Health GUIDE Partner Organization Agreement_CATCH.pdf</t>
+          <t>DPP SupplierAgreementGeneral CATCH FL03.13.26.docx</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2347,7 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>CATCH HHD MSA Final.docx</t>
+          <t>Harmonic Health GUIDE Partner Organization Agreement_CATCH.pdf</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2367,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>CATCH Greater Houston PSA 2025-2030,CW2595700 - signed.pdf</t>
+          <t>CATCH HHD MSA Final.docx</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2387,7 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Harmonic_CATCH_Care_Management_Agreement_Final_12926docx.pdf</t>
+          <t>CATCH Greater Houston PSA 2025-2030,CW2595700 - signed.pdf</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2407,7 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>CATCH Care Transitions Operations Manual.pdf</t>
+          <t>Harmonic_CATCH_Care_Management_Agreement_Final_12926docx.pdf</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2427,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>Common Spirit 2026.pdf</t>
+          <t>CATCH Care Transitions Operations Manual.pdf</t>
         </is>
       </c>
     </row>
@@ -2322,14 +2447,34 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
+          <t>Common Spirit 2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:34:08</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
           <t>Cumulus Fully Executed Master Subscription Agreement.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A6:F6"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CATCH_Compliance_Dashboard.xlsx
+++ b/CATCH_Compliance_Dashboard.xlsx
@@ -2124,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2176,11 +2176,11 @@
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17 13:02:47</t>
+          <t>2026-06-17 13:15:16</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -2200,11 +2200,11 @@
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 12:34:08</t>
+          <t>2026-06-17 13:02:47</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
@@ -2218,56 +2218,60 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
+          <t>No changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:34:08</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>11 document change(s) detected</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Document Change Log</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Run #</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Date &amp; Time</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Change Type</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Document Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-17 12:34:08</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>CATCH Insurance Proposal from USI.pdf</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2291,7 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>CATCH_ISF_3526_FINALdocx.pdf</t>
+          <t>CATCH Insurance Proposal from USI.pdf</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2311,7 @@
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>CATCH and PrognosUS DUA FINAL 3.19.26.docx.pdf</t>
+          <t>CATCH_ISF_3526_FINALdocx.pdf</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>DPP SupplierAgreementGeneral CATCH FL03.13.26.docx</t>
+          <t>CATCH and PrognosUS DUA FINAL 3.19.26.docx.pdf</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2351,7 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Harmonic Health GUIDE Partner Organization Agreement_CATCH.pdf</t>
+          <t>DPP SupplierAgreementGeneral CATCH FL03.13.26.docx</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2371,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>CATCH HHD MSA Final.docx</t>
+          <t>Harmonic Health GUIDE Partner Organization Agreement_CATCH.pdf</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2391,7 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>CATCH Greater Houston PSA 2025-2030,CW2595700 - signed.pdf</t>
+          <t>CATCH HHD MSA Final.docx</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2411,7 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Harmonic_CATCH_Care_Management_Agreement_Final_12926docx.pdf</t>
+          <t>CATCH Greater Houston PSA 2025-2030,CW2595700 - signed.pdf</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2431,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>CATCH Care Transitions Operations Manual.pdf</t>
+          <t>Harmonic_CATCH_Care_Management_Agreement_Final_12926docx.pdf</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2451,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>Common Spirit 2026.pdf</t>
+          <t>CATCH Care Transitions Operations Manual.pdf</t>
         </is>
       </c>
     </row>
@@ -2467,14 +2471,34 @@
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
+          <t>Common Spirit 2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:34:08</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
           <t>Cumulus Fully Executed Master Subscription Agreement.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
